--- a/plantillas/plantilla_checklist.xlsx
+++ b/plantillas/plantilla_checklist.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de Cumplimiento (✅ / ⚠️ / ❌)</t>
+          <t>Nivel de Cumplimiento (Cumple / Parcial)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
